--- a/pricing/商务成品/对内/云MaaS-上游折扣.xlsx
+++ b/pricing/商务成品/对内/云MaaS-上游折扣.xlsx
@@ -1,385 +1,230 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="13020"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29400" windowHeight="13020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="云MaaS" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="云MaaS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
-  <si>
-    <t>上游</t>
-  </si>
-  <si>
-    <t>原价折扣</t>
-  </si>
-  <si>
-    <t>包含模型</t>
-  </si>
-  <si>
-    <t>站点</t>
-  </si>
-  <si>
-    <t>Azure</t>
-  </si>
-  <si>
-    <t>6.5折</t>
-  </si>
-  <si>
-    <t>GPT：gpt-5、gpt-5-nano、gpt-5.1、gpt-5.2、gpt-5.3-codex、gpt-5.4、gpt-5.4-mini、gpt-5.4-nano、gpt-5.4-pro、gpt-5.5、gpt-5.6-luna、gpt-5.6-sol、gpt-5.6-terra
-GPT Image：gpt-image-2</t>
-  </si>
-  <si>
-    <t>海外</t>
-  </si>
-  <si>
-    <t>Google Cloud</t>
-  </si>
-  <si>
-    <t>7.5折</t>
-  </si>
-  <si>
-    <t>Gemini：gemini-2.5-flash、gemini-2.5-flash-lite、gemini-2.5-pro、gemini-3-flash-preview、gemini-3.1-flash-lite、gemini-3.1-pro-preview、gemini-3.5-flash、gemini-3.5-flash-lite、gemini-3.6-flash、gemini-3.7-flash
-Gemini Image：gemini-2.5-flash-image、gemini-3.1-flash-image、gemini-3.1-flash-lite-image
-Veo：veo-3.1、veo-3.1-fast、veo-3.1-lite
-Omni：gemini-omni-flash-preview</t>
-  </si>
-  <si>
-    <t>阿里云百炼-国内</t>
-  </si>
-  <si>
-    <t>5折</t>
-  </si>
-  <si>
-    <t>GLM-5.2：glm-5.2</t>
-  </si>
-  <si>
-    <t>中国站</t>
-  </si>
-  <si>
-    <t>6折</t>
-  </si>
-  <si>
-    <t>Qwen：qwen-flash、qwen-plus、qwen-max、qwen-turbo、qwen3.5-flash、qwen3.5-plus、qwen3.6-flash、qwen3.6-plus、qwen3.7-flash、qwen3.7-plus、qwen3.7-max、qwen3.8-max
-HH1.0：happyhorse-1.0、happyhorse-1.0-video-edit
-wan3.0：wan3.0-standard</t>
-  </si>
-  <si>
-    <t>7折</t>
-  </si>
-  <si>
-    <t>DeepSeek：deepseek-v3.2
-Kimi：kimi-k2.5、kimi-k2.6、kimi-k2.7-code
-MiniMax：minimax-m2.5、minimax-m2.7、minimax-m3
-wan2.7：wan2.7
-wan3.0：wan3.0-prime
-image-3.0：image-3.0</t>
-  </si>
-  <si>
-    <t>4折</t>
-  </si>
-  <si>
-    <t>HH1.1：happyhorse-1.1</t>
-  </si>
-  <si>
-    <t>阿里云百炼-国际</t>
-  </si>
-  <si>
-    <t>DeepSeek：deepseek-v4-flash-fast
-GLM-5.2：glm-5.2
-Qwen：qwen3.7-flash、qwen3.7-plus、qwen3.7-max、qwen3.8-max
-HH1.1：happyhorse-1.1</t>
-  </si>
-  <si>
-    <t>国际站</t>
-  </si>
-  <si>
-    <t>HH1.0：happyhorse-1.0-video-edit</t>
-  </si>
-  <si>
-    <t>AWS</t>
-  </si>
-  <si>
-    <t>7.8折</t>
-  </si>
-  <si>
-    <t>Claude Opus：claude-opus-4-6、claude-opus-4-7、claude-opus-4-8、claude-opus-5
-Claude Sonnet：claude-sonnet-4-6、claude-sonnet-5
-Claude Fable：claude-fable-5</t>
-  </si>
-  <si>
-    <t>字节·即梦</t>
-  </si>
-  <si>
-    <t>3.4折</t>
-  </si>
-  <si>
-    <t>Seedance：seedance-2.0-mini-overseas-hc-os</t>
-  </si>
-  <si>
-    <t>6.4折</t>
-  </si>
-  <si>
-    <t>Seedance：seedance-2.0-fast-hc-os</t>
-  </si>
-  <si>
-    <t>8.5折</t>
-  </si>
-  <si>
-    <t>Seedance：seedance-2.0-overseas-hc-os</t>
-  </si>
-  <si>
-    <t>Seedance：seedance-2.0-os</t>
-  </si>
-  <si>
-    <t>MiniMax</t>
-  </si>
-  <si>
-    <t>MiniMax：minimax-h3</t>
-  </si>
-  <si>
-    <t>Vidu</t>
-  </si>
-  <si>
-    <t>5.5折</t>
-  </si>
-  <si>
-    <t>Vidu Q2：viduq2、viduq2-pro、viduq2-turbo
-Vidu Q3：viduq3、viduq3-mix、viduq3-pro、viduq3-pro-fast、viduq3-turbo</t>
-  </si>
-  <si>
-    <t>xAI</t>
-  </si>
-  <si>
-    <t>3.2折</t>
-  </si>
-  <si>
-    <t>Grok：grok-imagine-video-1.5</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
-    <font>
-      <sz val="11"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="29">
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF263238"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="PingFang SC"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <b val="1"/>
       <color rgb="FF263238"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="PingFang SC"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC62828"/>
+      <color rgb="FF263238"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="PingFang SC"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF263238"/>
+      <b val="1"/>
+      <color rgb="FFC62828"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="PingFang SC"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <color rgb="FF263238"/>
       <sz val="10"/>
+    </font>
+    <font>
       <name val="PingFang SC"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <color rgb="00713F12"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <color rgb="001D2939"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="38">
-    <fill>
-      <patternFill patternType="none"/>
+  <fills count="40">
+    <fill>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -600,8 +445,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
+        <bgColor rgb="FFFEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B4F72"/>
+        <bgColor rgb="FF1B4F72"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -746,222 +603,257 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCFD8DC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D5DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D5DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D5DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D5DD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="29">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyBorder="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyFill="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyFill="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyFill="1" applyFont="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="13" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1017,11 +909,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1345,239 +1300,455 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.8359375" customWidth="1"/>
-    <col min="2" max="2" width="10.8359375" customWidth="1"/>
-    <col min="3" max="3" width="78" customWidth="1"/>
-    <col min="4" max="4" width="14.8359375" customWidth="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" ht="48" customHeight="1" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" ht="110" customHeight="1" spans="1:4">
-      <c r="A3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" ht="96" customHeight="1" spans="1:4">
-      <c r="A4" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="85" customHeight="1" spans="1:4">
-      <c r="A5" s="14"/>
-      <c r="B5" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="103" customHeight="1" spans="1:4">
-      <c r="A6" s="14"/>
-      <c r="B6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="1:4">
-      <c r="A7" s="15"/>
-      <c r="B7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" ht="84" customHeight="1" spans="1:4">
-      <c r="A8" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1" spans="1:4">
-      <c r="A9" s="15"/>
-      <c r="B9" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:4">
-      <c r="A11" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:4">
-      <c r="A12" s="22"/>
-      <c r="B12" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:4">
-      <c r="A13" s="22"/>
-      <c r="B13" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:4">
-      <c r="A14" s="23"/>
-      <c r="B14" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:4">
-      <c r="A15" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1" spans="1:4">
-      <c r="A16" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>7</v>
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>本页记录云 MaaS 上游折扣对照变更（新→旧）。手改「云MaaS」页后请在本页顶上补一行。上传后台不等于写线上刊例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="inlineStr">
+        <is>
+          <t>更新说明</t>
+        </is>
+      </c>
+      <c r="D2" s="26" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>2026.9.20</t>
+        </is>
+      </c>
+      <c r="B3" s="27" t="inlineStr">
+        <is>
+          <t>总册</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>启用「更新」累积日志（与商务总册同结构）</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>云MaaS · 首启</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col width="18.8359375" customWidth="1" min="1" max="1"/>
+    <col width="10.8359375" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="14.8359375" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>上游</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>原价折扣</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>包含模型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>站点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>6.5折</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>GPT：gpt-5、gpt-5-nano、gpt-5.1、gpt-5.2、gpt-5.3-codex、gpt-5.4、gpt-5.4-mini、gpt-5.4-nano、gpt-5.4-pro、gpt-5.5、gpt-5.6-luna、gpt-5.6-sol、gpt-5.6-terra
+GPT Image：gpt-image-2</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>海外</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="110" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>7.5折</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Gemini：gemini-2.5-flash、gemini-2.5-flash-lite、gemini-2.5-pro、gemini-3-flash-preview、gemini-3.1-flash-lite、gemini-3.1-pro-preview、gemini-3.5-flash、gemini-3.5-flash-lite、gemini-3.6-flash、gemini-3.7-flash
+Gemini Image：gemini-2.5-flash-image、gemini-3.1-flash-image、gemini-3.1-flash-lite-image
+Veo：veo-3.1、veo-3.1-fast、veo-3.1-lite
+Omni：gemini-omni-flash-preview</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>海外</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="96" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>阿里云百炼-国内</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>5折</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>GLM-5.2：glm-5.2</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>中国站</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="85" customHeight="1">
+      <c r="A5" s="14" t="n"/>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>6折</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Qwen：qwen-flash、qwen-plus、qwen-max、qwen-turbo、qwen3.5-flash、qwen3.5-plus、qwen3.6-flash、qwen3.6-plus、qwen3.7-flash、qwen3.7-plus、qwen3.7-max、qwen3.8-max
+HH1.0：happyhorse-1.0、happyhorse-1.0-video-edit
+wan3.0：wan3.0-standard</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>中国站</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="103" customHeight="1">
+      <c r="A6" s="14" t="n"/>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>7折</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>DeepSeek：deepseek-v3.2
+Kimi：kimi-k2.5、kimi-k2.6、kimi-k2.7-code
+MiniMax：minimax-m2.5、minimax-m2.7、minimax-m3
+wan2.7：wan2.7
+wan3.0：wan3.0-prime
+image-3.0：image-3.0</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>中国站</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>4折</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>HH1.1：happyhorse-1.1</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>中国站</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="84" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>阿里云百炼-国际</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>7折</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>DeepSeek：deepseek-v4-flash-fast
+GLM-5.2：glm-5.2
+Qwen：qwen3.7-flash、qwen3.7-plus、qwen3.7-max、qwen3.8-max
+HH1.1：happyhorse-1.1</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>国际站</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>6折</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>HH1.0：happyhorse-1.0-video-edit</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>国际站</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>7.8折</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Claude Opus：claude-opus-4-6、claude-opus-4-7、claude-opus-4-8、claude-opus-5
+Claude Sonnet：claude-sonnet-4-6、claude-sonnet-5
+Claude Fable：claude-fable-5</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>海外</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>字节·即梦</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>3.4折</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>Seedance：seedance-2.0-mini-overseas-hc-os</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>海外</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="14" t="n"/>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>6.4折</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Seedance：seedance-2.0-fast-hc-os</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>海外</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="14" t="n"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>8.5折</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>Seedance：seedance-2.0-overseas-hc-os</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>海外</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>8.5折</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>Seedance：seedance-2.0-os</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>中国站</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>8.5折</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>MiniMax：minimax-h3</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>海外</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Vidu</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>5.5折</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Vidu Q2：viduq2、viduq2-pro、viduq2-turbo
+Vidu Q3：viduq3、viduq3-mix、viduq3-pro、viduq3-pro-fast、viduq3-turbo</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>海外</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>3.2折</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Grok：grok-imagine-video-1.5</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>海外</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1587,6 +1758,5 @@
     <mergeCell ref="A11:A14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>